--- a/doc/IE_Data.xlsx
+++ b/doc/IE_Data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20386"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018BCF6D-AA1D-4420-853D-9E3AECE29431}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DFA1DB9-FC03-44F5-B998-69AC3B6B5D33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IE主表" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -889,10 +900,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="6">
-        <v>6000000</v>
+        <v>6400000</v>
       </c>
       <c r="C4" s="7">
-        <v>2200000</v>
+        <v>392000</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -911,10 +922,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="6">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7">
         <v>8</v>
-      </c>
-      <c r="C6" s="7">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -922,10 +933,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="8">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="C7" s="9">
-        <v>1</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -956,11 +967,11 @@
       </c>
       <c r="B10" s="6">
         <f>IFERROR(CEILING((B4/B5)/B7,1),0)</f>
-        <v>3958</v>
+        <v>4308</v>
       </c>
       <c r="C10" s="7">
         <f>IFERROR(CEILING((C4/C5)/C7,1),0)</f>
-        <v>3396</v>
+        <v>665</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15.75" thickBot="1">
@@ -969,11 +980,11 @@
       </c>
       <c r="B11" s="12">
         <f>IFERROR(CEILING((B10/B9)/B6,1),0)</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" s="13">
         <f>IFERROR(CEILING((C10/C9)/C6,1),0)</f>
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" thickBot="1"/>
@@ -1065,58 +1076,58 @@
         <v>50</v>
       </c>
       <c r="C15" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E15" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="21">
         <v>50</v>
       </c>
       <c r="G15" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H15" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I15" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="21">
-        <f t="shared" ref="J15:J40" si="0">IFERROR((IF(B15="",0,B15*C15*D15*E15)+IF(F15="",0,F15*G15*H15*I15))/(IF(B15="",0,C15*D15)+IF(F15="",0,G15*H15)),0)</f>
-        <v>152.55474452554745</v>
+        <f>IFERROR((IF(B15="",0,B15*C15*D15*E15)+IF(F15="",0,F15*G15*H15*I15))/(IF(B15="",0,C15*D15)+IF(F15="",0,G15*H15)),0)</f>
+        <v>113.04347826086956</v>
       </c>
       <c r="K15" s="6">
-        <f t="shared" ref="K15:K40" si="1">IFERROR(C15*D15,0)+IFERROR(G15*H15,0)</f>
-        <v>274</v>
+        <f t="shared" ref="K15:K40" si="0">IFERROR(C15*D15,0)+IFERROR(G15*H15,0)</f>
+        <v>184</v>
       </c>
       <c r="L15" s="22">
-        <f t="shared" ref="L15:L40" si="2">IFERROR(J15*K15/3600,0)</f>
-        <v>11.611111111111111</v>
+        <f t="shared" ref="L15:L40" si="1">IFERROR(J15*K15/3600,0)</f>
+        <v>5.7777777777777777</v>
       </c>
       <c r="M15" s="22">
         <f>IFERROR(L15/B8,0)</f>
-        <v>0.58055555555555549</v>
+        <v>0.28888888888888886</v>
       </c>
       <c r="N15" s="6">
         <v>1</v>
       </c>
       <c r="O15" s="8">
-        <f t="shared" ref="O15:O40" si="3">IFERROR(M15/N15,0)</f>
-        <v>0.58055555555555549</v>
+        <f t="shared" ref="O15:O40" si="2">IFERROR(M15/N15,0)</f>
+        <v>0.28888888888888886</v>
       </c>
       <c r="P15" s="6">
-        <f t="shared" ref="P15:P40" si="4">MAX(N15,CEILING(M15,1))</f>
+        <f t="shared" ref="P15:P40" si="3">MAX(N15,CEILING(M15,1))</f>
         <v>1</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" ref="Q15:Q40" si="5">IFERROR(M15/P15,0)</f>
-        <v>0.58055555555555549</v>
+        <f t="shared" ref="Q15:Q40" si="4">IFERROR(M15/P15,0)</f>
+        <v>0.28888888888888886</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1124,61 +1135,61 @@
         <v>28</v>
       </c>
       <c r="B16" s="21">
-        <v>67.400000000000006</v>
+        <v>146</v>
       </c>
       <c r="C16" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E16" s="6">
         <v>1</v>
       </c>
       <c r="F16" s="21">
-        <v>146</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="G16" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I16" s="6">
         <v>1</v>
       </c>
       <c r="J16" s="21">
+        <f t="shared" ref="J16:J40" si="5">IFERROR((IF(B16="",0,B16*C16*D16*E16)+IF(F16="",0,F16*G16*H16*I16))/(IF(B16="",0,C16*D16)+IF(F16="",0,G16*H16)),0)</f>
+        <v>135.74782608695651</v>
+      </c>
+      <c r="K16" s="6">
         <f t="shared" si="0"/>
-        <v>104.6919708029197</v>
-      </c>
-      <c r="K16" s="6">
+        <v>184</v>
+      </c>
+      <c r="L16" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L16" s="22">
-        <f t="shared" si="2"/>
-        <v>7.9682222222222219</v>
+        <v>6.9382222222222216</v>
       </c>
       <c r="M16" s="22">
         <f>IFERROR(L16/B8,0)</f>
-        <v>0.3984111111111111</v>
+        <v>0.34691111111111106</v>
       </c>
       <c r="N16" s="6">
         <v>2</v>
       </c>
       <c r="O16" s="8">
+        <f t="shared" si="2"/>
+        <v>0.17345555555555553</v>
+      </c>
+      <c r="P16" s="6">
         <f t="shared" si="3"/>
-        <v>0.19920555555555555</v>
-      </c>
-      <c r="P16" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q16" s="9">
-        <f t="shared" si="5"/>
-        <v>0.19920555555555555</v>
+        <v>0.17345555555555553</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1189,11 +1200,11 @@
         <v>75</v>
       </c>
       <c r="C17" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E17" s="6">
         <v>4</v>
@@ -1202,45 +1213,45 @@
         <v>60</v>
       </c>
       <c r="G17" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H17" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I17" s="6">
         <v>2</v>
       </c>
       <c r="J17" s="21">
+        <f t="shared" si="5"/>
+        <v>276.52173913043481</v>
+      </c>
+      <c r="K17" s="6">
         <f t="shared" si="0"/>
-        <v>214.5985401459854</v>
-      </c>
-      <c r="K17" s="6">
+        <v>184</v>
+      </c>
+      <c r="L17" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L17" s="22">
-        <f t="shared" si="2"/>
-        <v>16.333333333333332</v>
+        <v>14.133333333333335</v>
       </c>
       <c r="M17" s="22">
         <f>IFERROR(L17/B8,0)</f>
-        <v>0.81666666666666665</v>
+        <v>0.70666666666666678</v>
       </c>
       <c r="N17" s="6">
         <v>2</v>
       </c>
       <c r="O17" s="8">
+        <f t="shared" si="2"/>
+        <v>0.35333333333333339</v>
+      </c>
+      <c r="P17" s="6">
         <f t="shared" si="3"/>
-        <v>0.40833333333333333</v>
-      </c>
-      <c r="P17" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q17" s="9">
-        <f t="shared" si="5"/>
-        <v>0.40833333333333333</v>
+        <v>0.35333333333333339</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1251,58 +1262,58 @@
         <v>25</v>
       </c>
       <c r="C18" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E18" s="6">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F18" s="21">
         <v>25</v>
       </c>
       <c r="G18" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H18" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I18" s="6">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J18" s="21">
+        <f t="shared" si="5"/>
+        <v>297.82608695652175</v>
+      </c>
+      <c r="K18" s="6">
         <f t="shared" si="0"/>
-        <v>366.97080291970804</v>
-      </c>
-      <c r="K18" s="6">
+        <v>184</v>
+      </c>
+      <c r="L18" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L18" s="22">
-        <f t="shared" si="2"/>
-        <v>27.930555555555557</v>
+        <v>15.222222222222221</v>
       </c>
       <c r="M18" s="22">
         <f>IFERROR(L18/B8,0)</f>
-        <v>1.3965277777777778</v>
+        <v>0.76111111111111107</v>
       </c>
       <c r="N18" s="6">
         <v>2</v>
       </c>
       <c r="O18" s="8">
+        <f t="shared" si="2"/>
+        <v>0.38055555555555554</v>
+      </c>
+      <c r="P18" s="6">
         <f t="shared" si="3"/>
-        <v>0.69826388888888891</v>
-      </c>
-      <c r="P18" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q18" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q18" s="9">
-        <f t="shared" si="5"/>
-        <v>0.69826388888888891</v>
+        <v>0.38055555555555554</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1310,61 +1321,61 @@
         <v>31</v>
       </c>
       <c r="B19" s="21">
-        <v>19.329999999999998</v>
+        <v>19.3</v>
       </c>
       <c r="C19" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E19" s="6">
         <v>5</v>
       </c>
       <c r="F19" s="21">
-        <v>19.329999999999998</v>
+        <v>19.3</v>
       </c>
       <c r="G19" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H19" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I19" s="6">
         <v>5</v>
       </c>
       <c r="J19" s="21">
+        <f t="shared" si="5"/>
+        <v>96.5</v>
+      </c>
+      <c r="K19" s="6">
         <f t="shared" si="0"/>
-        <v>96.649999999999991</v>
-      </c>
-      <c r="K19" s="6">
+        <v>184</v>
+      </c>
+      <c r="L19" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L19" s="22">
-        <f t="shared" si="2"/>
-        <v>7.3561388888888883</v>
+        <v>4.9322222222222223</v>
       </c>
       <c r="M19" s="22">
         <f>IFERROR(L19/B8,0)</f>
-        <v>0.36780694444444439</v>
+        <v>0.24661111111111111</v>
       </c>
       <c r="N19" s="6">
         <v>1</v>
       </c>
       <c r="O19" s="8">
+        <f t="shared" si="2"/>
+        <v>0.24661111111111111</v>
+      </c>
+      <c r="P19" s="6">
         <f t="shared" si="3"/>
-        <v>0.36780694444444439</v>
-      </c>
-      <c r="P19" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q19" s="9">
-        <f t="shared" si="5"/>
-        <v>0.36780694444444439</v>
+        <v>0.24661111111111111</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1372,61 +1383,61 @@
         <v>32</v>
       </c>
       <c r="B20" s="21">
-        <v>168.75</v>
+        <v>135</v>
       </c>
       <c r="C20" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E20" s="6">
         <v>4</v>
       </c>
       <c r="F20" s="21">
-        <v>135</v>
+        <v>168.8</v>
       </c>
       <c r="G20" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H20" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I20" s="6">
         <v>4</v>
       </c>
       <c r="J20" s="21">
+        <f t="shared" si="5"/>
+        <v>557.63478260869567</v>
+      </c>
+      <c r="K20" s="6">
         <f t="shared" si="0"/>
-        <v>610.94890510948903</v>
-      </c>
-      <c r="K20" s="6">
+        <v>184</v>
+      </c>
+      <c r="L20" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L20" s="22">
-        <f t="shared" si="2"/>
-        <v>46.5</v>
+        <v>28.501333333333335</v>
       </c>
       <c r="M20" s="22">
         <f>IFERROR(L20/B8,0)</f>
-        <v>2.3250000000000002</v>
+        <v>1.4250666666666667</v>
       </c>
       <c r="N20" s="6">
         <v>3</v>
       </c>
       <c r="O20" s="8">
+        <f t="shared" si="2"/>
+        <v>0.47502222222222223</v>
+      </c>
+      <c r="P20" s="6">
         <f t="shared" si="3"/>
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="P20" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="9">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="Q20" s="9">
-        <f t="shared" si="5"/>
-        <v>0.77500000000000002</v>
+        <v>0.47502222222222223</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1437,58 +1448,58 @@
         <v>45</v>
       </c>
       <c r="C21" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" s="21">
         <v>45</v>
       </c>
       <c r="G21" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H21" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I21" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="21">
+        <f t="shared" si="5"/>
+        <v>140.86956521739131</v>
+      </c>
+      <c r="K21" s="6">
         <f t="shared" si="0"/>
-        <v>158.64963503649636</v>
-      </c>
-      <c r="K21" s="6">
+        <v>184</v>
+      </c>
+      <c r="L21" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L21" s="22">
-        <f t="shared" si="2"/>
-        <v>12.074999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M21" s="22">
         <f>IFERROR(L21/B8,0)</f>
-        <v>0.60375000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="N21" s="6">
         <v>1</v>
       </c>
       <c r="O21" s="8">
+        <f t="shared" si="2"/>
+        <v>0.36</v>
+      </c>
+      <c r="P21" s="6">
         <f t="shared" si="3"/>
-        <v>0.60375000000000001</v>
-      </c>
-      <c r="P21" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q21" s="9">
-        <f t="shared" si="5"/>
-        <v>0.60375000000000001</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -1496,61 +1507,61 @@
         <v>34</v>
       </c>
       <c r="B22" s="21">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C22" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D22" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E22" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="21">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G22" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H22" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I22" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" s="21">
+        <f t="shared" si="5"/>
+        <v>350.08695652173913</v>
+      </c>
+      <c r="K22" s="6">
         <f t="shared" si="0"/>
-        <v>321.67883211678833</v>
-      </c>
-      <c r="K22" s="6">
+        <v>184</v>
+      </c>
+      <c r="L22" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L22" s="22">
-        <f t="shared" si="2"/>
-        <v>24.483333333333334</v>
+        <v>17.893333333333334</v>
       </c>
       <c r="M22" s="22">
         <f>IFERROR(L22/B8,0)</f>
-        <v>1.2241666666666666</v>
+        <v>0.89466666666666672</v>
       </c>
       <c r="N22" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" s="8">
+        <f t="shared" si="2"/>
+        <v>0.89466666666666672</v>
+      </c>
+      <c r="P22" s="6">
         <f t="shared" si="3"/>
-        <v>0.61208333333333331</v>
-      </c>
-      <c r="P22" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q22" s="9">
-        <f t="shared" si="5"/>
-        <v>0.61208333333333331</v>
+        <v>0.89466666666666672</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -1558,61 +1569,61 @@
         <v>35</v>
       </c>
       <c r="B23" s="21">
-        <v>47.17</v>
+        <v>51.2</v>
       </c>
       <c r="C23" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E23" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" s="21">
-        <v>51.21</v>
+        <v>47.2</v>
       </c>
       <c r="G23" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H23" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I23" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J23" s="21">
+        <f t="shared" si="5"/>
+        <v>348.59130434782611</v>
+      </c>
+      <c r="K23" s="6">
         <f t="shared" si="0"/>
-        <v>318.81744525547447</v>
-      </c>
-      <c r="K23" s="6">
+        <v>184</v>
+      </c>
+      <c r="L23" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L23" s="22">
-        <f t="shared" si="2"/>
-        <v>24.265550000000005</v>
+        <v>17.81688888888889</v>
       </c>
       <c r="M23" s="22">
         <f>IFERROR(L23/B8,0)</f>
-        <v>1.2132775000000002</v>
+        <v>0.89084444444444455</v>
       </c>
       <c r="N23" s="6">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="O23" s="8">
+        <f t="shared" si="2"/>
+        <v>0.74237037037037046</v>
+      </c>
+      <c r="P23" s="6">
         <f t="shared" si="3"/>
-        <v>0.60663875000000012</v>
-      </c>
-      <c r="P23" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="Q23" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q23" s="9">
-        <f t="shared" si="5"/>
-        <v>0.60663875000000012</v>
+        <v>0.74237037037037046</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -1620,61 +1631,61 @@
         <v>36</v>
       </c>
       <c r="B24" s="21">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C24" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E24" s="6">
         <v>3</v>
       </c>
       <c r="F24" s="21">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="G24" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H24" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I24" s="6">
         <v>3</v>
       </c>
       <c r="J24" s="21">
+        <f t="shared" si="5"/>
+        <v>98.347826086956516</v>
+      </c>
+      <c r="K24" s="6">
         <f t="shared" si="0"/>
-        <v>132.72262773722628</v>
-      </c>
-      <c r="K24" s="6">
+        <v>184</v>
+      </c>
+      <c r="L24" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L24" s="22">
-        <f t="shared" si="2"/>
-        <v>10.101666666666667</v>
+        <v>5.0266666666666664</v>
       </c>
       <c r="M24" s="22">
         <f>IFERROR(L24/B8,0)</f>
-        <v>0.50508333333333333</v>
+        <v>0.2513333333333333</v>
       </c>
       <c r="N24" s="6">
         <v>1</v>
       </c>
       <c r="O24" s="8">
+        <f t="shared" si="2"/>
+        <v>0.2513333333333333</v>
+      </c>
+      <c r="P24" s="6">
         <f t="shared" si="3"/>
-        <v>0.50508333333333333</v>
-      </c>
-      <c r="P24" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q24" s="9">
-        <f t="shared" si="5"/>
-        <v>0.50508333333333333</v>
+        <v>0.2513333333333333</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -1685,58 +1696,58 @@
         <v>11.6</v>
       </c>
       <c r="C25" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E25" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="21">
         <v>11.6</v>
       </c>
       <c r="G25" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H25" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I25" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" s="21">
+        <f t="shared" si="5"/>
+        <v>33.286956521739128</v>
+      </c>
+      <c r="K25" s="6">
         <f t="shared" si="0"/>
-        <v>28.703649635036495</v>
-      </c>
-      <c r="K25" s="6">
+        <v>184</v>
+      </c>
+      <c r="L25" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L25" s="22">
-        <f t="shared" si="2"/>
-        <v>2.1846666666666663</v>
+        <v>1.7013333333333331</v>
       </c>
       <c r="M25" s="22">
         <f>IFERROR(L25/B8,0)</f>
-        <v>0.10923333333333332</v>
+        <v>8.5066666666666652E-2</v>
       </c>
       <c r="N25" s="6">
         <v>1</v>
       </c>
       <c r="O25" s="8">
+        <f t="shared" si="2"/>
+        <v>8.5066666666666652E-2</v>
+      </c>
+      <c r="P25" s="6">
         <f t="shared" si="3"/>
-        <v>0.10923333333333332</v>
-      </c>
-      <c r="P25" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q25" s="9">
-        <f t="shared" si="5"/>
-        <v>0.10923333333333332</v>
+        <v>8.5066666666666652E-2</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -1744,61 +1755,61 @@
         <v>38</v>
       </c>
       <c r="B26" s="21">
-        <v>92.5</v>
+        <v>66.5</v>
       </c>
       <c r="C26" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E26" s="6">
         <v>4</v>
       </c>
       <c r="F26" s="21">
-        <v>66.5</v>
+        <v>92.5</v>
       </c>
       <c r="G26" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H26" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I26" s="6">
         <v>4</v>
       </c>
       <c r="J26" s="21">
+        <f t="shared" si="5"/>
+        <v>279.56521739130437</v>
+      </c>
+      <c r="K26" s="6">
         <f t="shared" si="0"/>
-        <v>320.65693430656933</v>
-      </c>
-      <c r="K26" s="6">
+        <v>184</v>
+      </c>
+      <c r="L26" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L26" s="22">
-        <f t="shared" si="2"/>
-        <v>24.405555555555555</v>
+        <v>14.288888888888891</v>
       </c>
       <c r="M26" s="22">
         <f>IFERROR(L26/B8,0)</f>
-        <v>1.2202777777777778</v>
+        <v>0.71444444444444455</v>
       </c>
       <c r="N26" s="6">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O26" s="8">
+        <f t="shared" si="2"/>
+        <v>0.59537037037037044</v>
+      </c>
+      <c r="P26" s="6">
         <f t="shared" si="3"/>
-        <v>1.2202777777777778</v>
-      </c>
-      <c r="P26" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="Q26" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q26" s="9">
-        <f t="shared" si="5"/>
-        <v>0.6101388888888889</v>
+        <v>0.59537037037037044</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -1809,58 +1820,58 @@
         <v>25</v>
       </c>
       <c r="C27" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E27" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="21">
         <v>25</v>
       </c>
       <c r="G27" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H27" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I27" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="21">
+        <f t="shared" si="5"/>
+        <v>78.260869565217391</v>
+      </c>
+      <c r="K27" s="6">
         <f t="shared" si="0"/>
-        <v>88.138686131386862</v>
-      </c>
-      <c r="K27" s="6">
+        <v>184</v>
+      </c>
+      <c r="L27" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L27" s="22">
-        <f t="shared" si="2"/>
-        <v>6.708333333333333</v>
+        <v>4</v>
       </c>
       <c r="M27" s="22">
         <f>IFERROR(L27/B8,0)</f>
-        <v>0.33541666666666664</v>
+        <v>0.2</v>
       </c>
       <c r="N27" s="6">
         <v>1</v>
       </c>
       <c r="O27" s="8">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="P27" s="6">
         <f t="shared" si="3"/>
-        <v>0.33541666666666664</v>
-      </c>
-      <c r="P27" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q27" s="9">
-        <f t="shared" si="5"/>
-        <v>0.33541666666666664</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -1868,61 +1879,61 @@
         <v>40</v>
       </c>
       <c r="B28" s="21">
-        <v>13.33</v>
+        <v>15.4</v>
       </c>
       <c r="C28" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D28" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E28" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F28" s="21">
-        <v>15.43</v>
+        <v>13.3</v>
       </c>
       <c r="G28" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H28" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I28" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J28" s="21">
+        <f t="shared" si="5"/>
+        <v>109.35217391304347</v>
+      </c>
+      <c r="K28" s="6">
         <f t="shared" si="0"/>
-        <v>114.29554744525548</v>
-      </c>
-      <c r="K28" s="6">
+        <v>184</v>
+      </c>
+      <c r="L28" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L28" s="22">
-        <f t="shared" si="2"/>
-        <v>8.6991611111111116</v>
+        <v>5.5891111111111105</v>
       </c>
       <c r="M28" s="22">
         <f>IFERROR(L28/B8,0)</f>
-        <v>0.43495805555555556</v>
+        <v>0.27945555555555551</v>
       </c>
       <c r="N28" s="6">
         <v>1</v>
       </c>
       <c r="O28" s="8">
+        <f t="shared" si="2"/>
+        <v>0.27945555555555551</v>
+      </c>
+      <c r="P28" s="6">
         <f t="shared" si="3"/>
-        <v>0.43495805555555556</v>
-      </c>
-      <c r="P28" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q28" s="9">
-        <f t="shared" si="5"/>
-        <v>0.43495805555555556</v>
+        <v>0.27945555555555551</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -1930,61 +1941,61 @@
         <v>41</v>
       </c>
       <c r="B29" s="21">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="C29" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E29" s="6">
         <v>3</v>
       </c>
       <c r="F29" s="21">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G29" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H29" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I29" s="6">
         <v>3</v>
       </c>
       <c r="J29" s="21">
+        <f t="shared" si="5"/>
+        <v>223.04347826086956</v>
+      </c>
+      <c r="K29" s="6">
         <f t="shared" si="0"/>
-        <v>244.37956204379563</v>
-      </c>
-      <c r="K29" s="6">
+        <v>184</v>
+      </c>
+      <c r="L29" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L29" s="22">
-        <f t="shared" si="2"/>
-        <v>18.600000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="M29" s="22">
         <f>IFERROR(L29/B8,0)</f>
-        <v>0.93</v>
+        <v>0.57000000000000006</v>
       </c>
       <c r="N29" s="6">
         <v>1</v>
       </c>
       <c r="O29" s="8">
+        <f t="shared" si="2"/>
+        <v>0.57000000000000006</v>
+      </c>
+      <c r="P29" s="6">
         <f t="shared" si="3"/>
-        <v>0.93</v>
-      </c>
-      <c r="P29" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q29" s="9">
-        <f t="shared" si="5"/>
-        <v>0.93</v>
+        <v>0.57000000000000006</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -1992,61 +2003,61 @@
         <v>42</v>
       </c>
       <c r="B30" s="21">
-        <v>27.75</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="C30" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D30" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E30" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" s="21">
-        <v>32.25</v>
+        <v>27.8</v>
       </c>
       <c r="G30" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H30" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I30" s="6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J30" s="21">
+        <f t="shared" si="5"/>
+        <v>263.66086956521741</v>
+      </c>
+      <c r="K30" s="6">
         <f t="shared" si="0"/>
-        <v>283.54927007299273</v>
-      </c>
-      <c r="K30" s="6">
+        <v>184</v>
+      </c>
+      <c r="L30" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L30" s="22">
-        <f t="shared" si="2"/>
-        <v>21.581250000000001</v>
+        <v>13.476000000000001</v>
       </c>
       <c r="M30" s="22">
         <f>IFERROR(L30/B8,0)</f>
-        <v>1.0790625</v>
+        <v>0.67380000000000007</v>
       </c>
       <c r="N30" s="6">
         <v>1</v>
       </c>
       <c r="O30" s="8">
+        <f t="shared" si="2"/>
+        <v>0.67380000000000007</v>
+      </c>
+      <c r="P30" s="6">
         <f t="shared" si="3"/>
-        <v>1.0790625</v>
-      </c>
-      <c r="P30" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q30" s="9">
-        <f t="shared" si="5"/>
-        <v>0.53953125000000002</v>
+        <v>0.67380000000000007</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -2054,61 +2065,61 @@
         <v>43</v>
       </c>
       <c r="B31" s="21">
-        <v>540</v>
+        <v>180</v>
       </c>
       <c r="C31" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D31" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E31" s="6">
         <v>1</v>
       </c>
       <c r="F31" s="21">
-        <v>180</v>
+        <v>540</v>
       </c>
       <c r="G31" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H31" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I31" s="6">
         <v>1</v>
       </c>
       <c r="J31" s="21">
+        <f t="shared" si="5"/>
+        <v>226.95652173913044</v>
+      </c>
+      <c r="K31" s="6">
         <f t="shared" si="0"/>
-        <v>369.19708029197079</v>
-      </c>
-      <c r="K31" s="6">
+        <v>184</v>
+      </c>
+      <c r="L31" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L31" s="22">
-        <f t="shared" si="2"/>
-        <v>28.1</v>
+        <v>11.6</v>
       </c>
       <c r="M31" s="22">
         <f>IFERROR(L31/B8,0)</f>
-        <v>1.405</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="N31" s="6">
         <v>2</v>
       </c>
       <c r="O31" s="8">
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P31" s="6">
         <f t="shared" si="3"/>
-        <v>0.70250000000000001</v>
-      </c>
-      <c r="P31" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q31" s="9">
-        <f t="shared" si="5"/>
-        <v>0.70250000000000001</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -2116,61 +2127,61 @@
         <v>44</v>
       </c>
       <c r="B32" s="21">
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="C32" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D32" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E32" s="6">
         <v>1</v>
       </c>
       <c r="F32" s="21">
-        <v>1500</v>
+        <v>2100</v>
       </c>
       <c r="G32" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H32" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I32" s="6">
         <v>1</v>
       </c>
       <c r="J32" s="21">
+        <f t="shared" si="5"/>
+        <v>1578.2608695652175</v>
+      </c>
+      <c r="K32" s="6">
         <f t="shared" si="0"/>
-        <v>1815.3284671532847</v>
-      </c>
-      <c r="K32" s="6">
+        <v>184</v>
+      </c>
+      <c r="L32" s="22">
         <f t="shared" si="1"/>
-        <v>274</v>
-      </c>
-      <c r="L32" s="22">
-        <f t="shared" si="2"/>
-        <v>138.16666666666666</v>
+        <v>80.666666666666671</v>
       </c>
       <c r="M32" s="22">
         <f>IFERROR(L32/B8,0)</f>
-        <v>6.9083333333333332</v>
+        <v>4.0333333333333332</v>
       </c>
       <c r="N32" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O32" s="8">
+        <f t="shared" si="2"/>
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="P32" s="6">
         <f t="shared" si="3"/>
-        <v>0.7675925925925926</v>
-      </c>
-      <c r="P32" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="9">
         <f t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="Q32" s="9">
-        <f t="shared" si="5"/>
-        <v>0.7675925925925926</v>
+        <v>0.50416666666666665</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -2181,11 +2192,11 @@
         <v>360</v>
       </c>
       <c r="C33" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D33" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E33" s="6">
         <v>1</v>
@@ -2194,39 +2205,39 @@
       <c r="G33" s="6"/>
       <c r="H33" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I33" s="6"/>
       <c r="J33" s="21">
+        <f t="shared" si="5"/>
+        <v>360</v>
+      </c>
+      <c r="K33" s="6">
         <f t="shared" si="0"/>
-        <v>360</v>
-      </c>
-      <c r="K33" s="6">
+        <v>160</v>
+      </c>
+      <c r="L33" s="22">
         <f t="shared" si="1"/>
-        <v>144</v>
-      </c>
-      <c r="L33" s="22">
-        <f t="shared" si="2"/>
-        <v>14.4</v>
+        <v>16</v>
       </c>
       <c r="M33" s="22">
         <f>IFERROR(L33/B8,0)</f>
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="N33" s="6">
         <v>1</v>
       </c>
       <c r="O33" s="8">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="P33" s="6">
         <f t="shared" si="3"/>
-        <v>0.72</v>
-      </c>
-      <c r="P33" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q33" s="9">
-        <f t="shared" si="5"/>
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -2234,14 +2245,14 @@
         <v>46</v>
       </c>
       <c r="B34" s="21">
-        <v>1209</v>
+        <v>985</v>
       </c>
       <c r="C34" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D34" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E34" s="6">
         <v>1</v>
@@ -2250,39 +2261,39 @@
       <c r="G34" s="6"/>
       <c r="H34" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="21">
+        <f t="shared" si="5"/>
+        <v>985</v>
+      </c>
+      <c r="K34" s="6">
         <f t="shared" si="0"/>
-        <v>1209</v>
-      </c>
-      <c r="K34" s="6">
+        <v>160</v>
+      </c>
+      <c r="L34" s="22">
         <f t="shared" si="1"/>
-        <v>144</v>
-      </c>
-      <c r="L34" s="22">
-        <f t="shared" si="2"/>
-        <v>48.36</v>
+        <v>43.777777777777779</v>
       </c>
       <c r="M34" s="22">
         <f>IFERROR(L34/B8,0)</f>
-        <v>2.4180000000000001</v>
+        <v>2.1888888888888891</v>
       </c>
       <c r="N34" s="6">
         <v>3</v>
       </c>
       <c r="O34" s="8">
+        <f t="shared" si="2"/>
+        <v>0.72962962962962974</v>
+      </c>
+      <c r="P34" s="6">
         <f t="shared" si="3"/>
-        <v>0.80600000000000005</v>
-      </c>
-      <c r="P34" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="9">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="Q34" s="9">
-        <f t="shared" si="5"/>
-        <v>0.80600000000000005</v>
+        <v>0.72962962962962974</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -2290,14 +2301,14 @@
         <v>47</v>
       </c>
       <c r="B35" s="21">
-        <v>8556</v>
+        <v>6367.2</v>
       </c>
       <c r="C35" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D35" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E35" s="6">
         <v>1</v>
@@ -2306,39 +2317,39 @@
       <c r="G35" s="6"/>
       <c r="H35" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="21">
+        <f t="shared" si="5"/>
+        <v>6367.2</v>
+      </c>
+      <c r="K35" s="6">
         <f t="shared" si="0"/>
-        <v>8556</v>
-      </c>
-      <c r="K35" s="6">
+        <v>160</v>
+      </c>
+      <c r="L35" s="22">
         <f t="shared" si="1"/>
-        <v>144</v>
-      </c>
-      <c r="L35" s="22">
-        <f t="shared" si="2"/>
-        <v>342.24</v>
+        <v>282.98666666666668</v>
       </c>
       <c r="M35" s="22">
         <f>IFERROR(L35/B8,0)</f>
-        <v>17.112000000000002</v>
+        <v>14.149333333333335</v>
       </c>
       <c r="N35" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O35" s="8">
+        <f t="shared" si="2"/>
+        <v>0.74470175438596498</v>
+      </c>
+      <c r="P35" s="6">
         <f t="shared" si="3"/>
-        <v>1.2222857142857144</v>
-      </c>
-      <c r="P35" s="6">
+        <v>19</v>
+      </c>
+      <c r="Q35" s="9">
         <f t="shared" si="4"/>
-        <v>18</v>
-      </c>
-      <c r="Q35" s="9">
-        <f t="shared" si="5"/>
-        <v>0.95066666666666677</v>
+        <v>0.74470175438596498</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -2349,52 +2360,52 @@
       <c r="C36" s="6"/>
       <c r="D36" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="21">
         <v>195</v>
       </c>
       <c r="G36" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H36" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I36" s="6">
         <v>1</v>
       </c>
       <c r="J36" s="21">
+        <f t="shared" si="5"/>
+        <v>195</v>
+      </c>
+      <c r="K36" s="6">
         <f t="shared" si="0"/>
-        <v>195</v>
-      </c>
-      <c r="K36" s="6">
+        <v>24</v>
+      </c>
+      <c r="L36" s="22">
         <f t="shared" si="1"/>
-        <v>130</v>
-      </c>
-      <c r="L36" s="22">
-        <f t="shared" si="2"/>
-        <v>7.041666666666667</v>
+        <v>1.3</v>
       </c>
       <c r="M36" s="22">
         <f>IFERROR(L36/B8,0)</f>
-        <v>0.35208333333333336</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="N36" s="6">
         <v>1</v>
       </c>
       <c r="O36" s="8">
+        <f t="shared" si="2"/>
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P36" s="6">
         <f t="shared" si="3"/>
-        <v>0.35208333333333336</v>
-      </c>
-      <c r="P36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q36" s="9">
-        <f t="shared" si="5"/>
-        <v>0.35208333333333336</v>
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -2405,52 +2416,52 @@
       <c r="C37" s="6"/>
       <c r="D37" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="21">
         <v>120</v>
       </c>
       <c r="G37" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H37" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I37" s="6">
         <v>1</v>
       </c>
       <c r="J37" s="21">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="K37" s="6">
         <f t="shared" si="0"/>
-        <v>120</v>
-      </c>
-      <c r="K37" s="6">
+        <v>24</v>
+      </c>
+      <c r="L37" s="22">
         <f t="shared" si="1"/>
-        <v>130</v>
-      </c>
-      <c r="L37" s="22">
-        <f t="shared" si="2"/>
-        <v>4.333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="M37" s="22">
         <f>IFERROR(L37/B8,0)</f>
-        <v>0.21666666666666665</v>
+        <v>0.04</v>
       </c>
       <c r="N37" s="6">
         <v>1</v>
       </c>
       <c r="O37" s="8">
+        <f t="shared" si="2"/>
+        <v>0.04</v>
+      </c>
+      <c r="P37" s="6">
         <f t="shared" si="3"/>
-        <v>0.21666666666666665</v>
-      </c>
-      <c r="P37" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q37" s="9">
-        <f t="shared" si="5"/>
-        <v>0.21666666666666665</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -2461,52 +2472,52 @@
       <c r="C38" s="6"/>
       <c r="D38" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="21">
         <v>457.5</v>
       </c>
       <c r="G38" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H38" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I38" s="6">
         <v>1</v>
       </c>
       <c r="J38" s="21">
+        <f t="shared" si="5"/>
+        <v>457.5</v>
+      </c>
+      <c r="K38" s="6">
         <f t="shared" si="0"/>
-        <v>457.5</v>
-      </c>
-      <c r="K38" s="6">
+        <v>24</v>
+      </c>
+      <c r="L38" s="22">
         <f t="shared" si="1"/>
-        <v>130</v>
-      </c>
-      <c r="L38" s="22">
-        <f t="shared" si="2"/>
-        <v>16.520833333333332</v>
+        <v>3.05</v>
       </c>
       <c r="M38" s="22">
         <f>IFERROR(L38/B8,0)</f>
-        <v>0.82604166666666656</v>
+        <v>0.1525</v>
       </c>
       <c r="N38" s="6">
         <v>2</v>
       </c>
       <c r="O38" s="8">
+        <f t="shared" si="2"/>
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="P38" s="6">
         <f t="shared" si="3"/>
-        <v>0.41302083333333328</v>
-      </c>
-      <c r="P38" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q38" s="9">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="Q38" s="9">
-        <f t="shared" si="5"/>
-        <v>0.41302083333333328</v>
+        <v>7.6249999999999998E-2</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -2517,52 +2528,52 @@
       <c r="C39" s="6"/>
       <c r="D39" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="21">
-        <v>312.75</v>
+        <v>312.8</v>
       </c>
       <c r="G39" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H39" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I39" s="6">
         <v>1</v>
       </c>
       <c r="J39" s="21">
+        <f t="shared" si="5"/>
+        <v>312.8</v>
+      </c>
+      <c r="K39" s="6">
         <f t="shared" si="0"/>
-        <v>312.75</v>
-      </c>
-      <c r="K39" s="6">
+        <v>24</v>
+      </c>
+      <c r="L39" s="22">
         <f t="shared" si="1"/>
-        <v>130</v>
-      </c>
-      <c r="L39" s="22">
-        <f t="shared" si="2"/>
-        <v>11.293749999999999</v>
+        <v>2.0853333333333337</v>
       </c>
       <c r="M39" s="22">
         <f>IFERROR(L39/B8,0)</f>
-        <v>0.56468750000000001</v>
+        <v>0.10426666666666669</v>
       </c>
       <c r="N39" s="6">
         <v>1</v>
       </c>
       <c r="O39" s="8">
+        <f t="shared" si="2"/>
+        <v>0.10426666666666669</v>
+      </c>
+      <c r="P39" s="6">
         <f t="shared" si="3"/>
-        <v>0.56468750000000001</v>
-      </c>
-      <c r="P39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="9">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q39" s="9">
-        <f t="shared" si="5"/>
-        <v>0.56468750000000001</v>
+        <v>0.10426666666666669</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -2573,52 +2584,52 @@
       <c r="C40" s="6"/>
       <c r="D40" s="22">
         <f>B11</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="21">
-        <v>4185</v>
+        <v>4276</v>
       </c>
       <c r="G40" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H40" s="22">
         <f>C11</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I40" s="6">
         <v>1</v>
       </c>
       <c r="J40" s="21">
+        <f t="shared" si="5"/>
+        <v>4276</v>
+      </c>
+      <c r="K40" s="6">
         <f t="shared" si="0"/>
-        <v>4185</v>
-      </c>
-      <c r="K40" s="6">
+        <v>24</v>
+      </c>
+      <c r="L40" s="22">
         <f t="shared" si="1"/>
-        <v>130</v>
-      </c>
-      <c r="L40" s="22">
-        <f t="shared" si="2"/>
-        <v>151.125</v>
+        <v>28.506666666666668</v>
       </c>
       <c r="M40" s="22">
         <f>IFERROR(L40/B8,0)</f>
-        <v>7.5562500000000004</v>
+        <v>1.4253333333333333</v>
       </c>
       <c r="N40" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O40" s="8">
+        <f t="shared" si="2"/>
+        <v>0.71266666666666667</v>
+      </c>
+      <c r="P40" s="6">
         <f t="shared" si="3"/>
-        <v>1.0794642857142858</v>
-      </c>
-      <c r="P40" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="9">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="Q40" s="9">
-        <f t="shared" si="5"/>
-        <v>0.94453125000000004</v>
+        <v>0.71266666666666667</v>
       </c>
     </row>
   </sheetData>
